--- a/business_forms/039_personnel_emergency_response_group_training_record_form--business_forms.xlsx
+++ b/business_forms/039_personnel_emergency_response_group_training_record_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,69 +515,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_1</t>
+          <t>training_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ประก 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the training date?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Date of the training</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_2</t>
+          <t>training_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Training Date</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the training time?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Time of the training</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_3</t>
+          <t>training_instructor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Training Time</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Who is the training instructor?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Name of the training instructor</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,110 +601,130 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_4</t>
+          <t>training_location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Training Instructor</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Where is the training location?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Location of the training</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_5</t>
+          <t>training_type_single</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the training type (single selection)?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select one option</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_6</t>
+          <t>training_type_yes_no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Training Location</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Is the training type 'Yes' or 'No'?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select one option</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_7</t>
+          <t>training_type_multiple</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Training Location</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What are the training types?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select multiple options</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_8</t>
+          <t>training_type_yes_no_multiple</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Training Location</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Is the training 'Yes' or 'No'?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select multiple options</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_9</t>
+          <t>duplicate_location_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Training Location</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Duplicate Location 1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Location of the training</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,133 +763,76 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_10</t>
+          <t>duplicate_location_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Training Location</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the training location?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Location of the training</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_11</t>
+          <t>duplicate_location_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Training Type</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Training Location</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Location of the training</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_12</t>
+          <t>duplicate_location_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Training Type</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Duplicate Location 4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Location of the training</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>personnel_emergency_response_group_training_record_form_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Training Type</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>personnel_emergency_response_group_training_record_form_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Training Type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>personnel_emergency_response_group_training_record_form_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Training Type</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -868,10 +847,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
@@ -896,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_11_choices</t>
+          <t>training_type_single_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -913,7 +892,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_11_choices</t>
+          <t>training_type_single_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -930,7 +909,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_11_choices</t>
+          <t>training_type_single_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,7 +926,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_11_choices</t>
+          <t>training_type_single_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -964,7 +943,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_11_choices</t>
+          <t>training_type_single_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -981,7 +960,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_12_choices</t>
+          <t>training_type_yes_no_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -998,7 +977,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_12_choices</t>
+          <t>training_type_yes_no_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,7 +994,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_13_choices</t>
+          <t>training_type_multiple_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1032,7 +1011,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_13_choices</t>
+          <t>training_type_multiple_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1028,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_13_choices</t>
+          <t>training_type_multiple_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1066,7 +1045,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_13_choices</t>
+          <t>training_type_multiple_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1083,7 +1062,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_13_choices</t>
+          <t>training_type_multiple_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1100,7 +1079,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_14_choices</t>
+          <t>training_type_yes_no_multiple_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1117,7 +1096,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>personnel_emergency_response_group_training_record_form_14_choices</t>
+          <t>training_type_yes_no_multiple_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1126,40 +1105,6 @@
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>personnel_emergency_response_group_training_record_form_15_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>personnel_emergency_response_group_training_record_form_15_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
